--- a/files/input/template.xlsx
+++ b/files/input/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zubin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramFiles\VM_OS\shared\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8447A86-D631-4428-8A4B-6ECBF9BEDFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E586A1-E38A-416E-B289-42569F7E72B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32160" yWindow="3315" windowWidth="21555" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="19">
   <si>
     <t>trade_id</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>End of the day total:</t>
+  </si>
+  <si>
+    <t>TitanBot</t>
   </si>
 </sst>
 </file>
@@ -203,7 +206,45 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -332,7 +373,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}" name="Table2" displayName="Table2" ref="E24:P30" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}" name="Table2" displayName="Table2" ref="E24:P30" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="E24:P30" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{728F177D-253D-43C0-9D08-1611929D397C}" name="trade_id"/>
@@ -353,7 +394,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}" name="Table26" displayName="Table26" ref="E5:P11" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}" name="Table26" displayName="Table26" ref="E5:P11" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="E5:P11" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{E22242C5-FE80-48C9-930E-50866008E382}" name="trade_id"/>
@@ -374,7 +415,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}" name="Table27" displayName="Table27" ref="E41:P48" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}" name="Table27" displayName="Table27" ref="E41:P48" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="E41:P48" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{43F6BD0D-9896-4A11-A4EF-1337EE02DDEA}" name="trade_id"/>
@@ -389,6 +430,27 @@
     <tableColumn id="10" xr3:uid="{D21B0723-35F2-4E4A-BFC0-8CBB7FFAC0C8}" name="timestamp"/>
     <tableColumn id="11" xr3:uid="{805D9AA6-FAD0-4A51-AD51-77AEB8BECF53}" name="qty"/>
     <tableColumn id="12" xr3:uid="{D0E2B8C5-B5B7-4C06-B3EC-F8AB0C576BAD}" name="amount"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}" name="Table274" displayName="Table274" ref="E62:P69" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="E62:P69" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{CED8C13A-4CD1-41D7-8452-F510512A6571}" name="trade_id"/>
+    <tableColumn id="2" xr3:uid="{86DBCD69-CBC5-4C50-A011-ECEC03FFA29C}" name="broker_order_id"/>
+    <tableColumn id="3" xr3:uid="{F519000C-67AD-44EC-9D43-B3F98260380F}" name="exchange_order_id"/>
+    <tableColumn id="4" xr3:uid="{B2098C9A-FA63-4E49-9C2C-3EC03CEC40AA}" name="instrument"/>
+    <tableColumn id="5" xr3:uid="{DE50AE83-DBE2-46C5-A474-7E4AC76316B2}" name="instrument_key"/>
+    <tableColumn id="6" xr3:uid="{A8D89147-922B-4E5C-9D25-9357DEACCC7E}" name="side"/>
+    <tableColumn id="7" xr3:uid="{E934EAFD-B95A-4B82-964F-541E6273935E}" name="entry"/>
+    <tableColumn id="8" xr3:uid="{92E46316-B608-488E-BA6F-6A1F724D5CDF}" name="exit"/>
+    <tableColumn id="9" xr3:uid="{5FB2A7E1-56BF-47C3-A39D-692E7D73EDFD}" name="trailed"/>
+    <tableColumn id="10" xr3:uid="{15676849-DA01-4E14-8C15-D80BD4EB3857}" name="timestamp"/>
+    <tableColumn id="11" xr3:uid="{9472537C-8D3F-44E2-8E6F-E70F64158E15}" name="qty"/>
+    <tableColumn id="12" xr3:uid="{BD311DD0-F1E1-4060-8C38-8C9EA5B490D9}" name="amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -657,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81522B13-2059-4C06-A47E-15A0BC3CF508}">
-  <dimension ref="D3:V59"/>
+  <dimension ref="D3:V80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
@@ -1051,13 +1113,135 @@
       <c r="O56" s="7"/>
       <c r="P56" s="7"/>
     </row>
-    <row r="59" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E59" s="5" t="s">
+    <row r="60" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+    </row>
+    <row r="62" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E62" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="O71" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E73" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="7"/>
+    </row>
+    <row r="75" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="7"/>
+    </row>
+    <row r="76" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
+      <c r="M76" s="7"/>
+      <c r="N76" s="7"/>
+      <c r="O76" s="7"/>
+      <c r="P76" s="7"/>
+    </row>
+    <row r="77" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
+      <c r="N77" s="7"/>
+      <c r="O77" s="7"/>
+      <c r="P77" s="7"/>
+    </row>
+    <row r="80" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E80" s="5" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="E60:P60"/>
+    <mergeCell ref="E74:P77"/>
     <mergeCell ref="E39:P39"/>
     <mergeCell ref="E53:P56"/>
     <mergeCell ref="E3:P3"/>
@@ -1066,10 +1250,11 @@
     <mergeCell ref="E34:P37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="3">
+  <tableParts count="4">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/files/input/template.xlsx
+++ b/files/input/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramFiles\VM_OS\shared\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E586A1-E38A-416E-B289-42569F7E72B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0288A32F-502F-46C9-BE70-BA408EE56C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="20">
   <si>
     <t>trade_id</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>TitanBot</t>
+  </si>
+  <si>
+    <t>Fibobot</t>
   </si>
 </sst>
 </file>
@@ -206,7 +209,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
     <dxf>
       <border outline="0">
         <bottom style="thin">
@@ -219,6 +222,44 @@
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -373,7 +414,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}" name="Table2" displayName="Table2" ref="E24:P30" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}" name="Table2" displayName="Table2" ref="E24:P30" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="E24:P30" xr:uid="{68D694CD-92E6-45B3-9118-CF9D8D8F57F6}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{728F177D-253D-43C0-9D08-1611929D397C}" name="trade_id"/>
@@ -394,7 +435,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}" name="Table26" displayName="Table26" ref="E5:P11" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}" name="Table26" displayName="Table26" ref="E5:P11" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="E5:P11" xr:uid="{FE86F7BC-FC81-4DD6-A8FC-A6D693112099}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{E22242C5-FE80-48C9-930E-50866008E382}" name="trade_id"/>
@@ -415,7 +456,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}" name="Table27" displayName="Table27" ref="E41:P48" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}" name="Table27" displayName="Table27" ref="E41:P48" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="E41:P48" xr:uid="{BF1137ED-730D-47DE-9126-2E5228BE5DBF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{43F6BD0D-9896-4A11-A4EF-1337EE02DDEA}" name="trade_id"/>
@@ -436,7 +477,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}" name="Table274" displayName="Table274" ref="E62:P69" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}" name="Table274" displayName="Table274" ref="E62:P69" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="E62:P69" xr:uid="{CF19F3F2-2B98-4A9C-9D3F-0DC68BB0761E}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{CED8C13A-4CD1-41D7-8452-F510512A6571}" name="trade_id"/>
@@ -451,6 +492,27 @@
     <tableColumn id="10" xr3:uid="{15676849-DA01-4E14-8C15-D80BD4EB3857}" name="timestamp"/>
     <tableColumn id="11" xr3:uid="{9472537C-8D3F-44E2-8E6F-E70F64158E15}" name="qty"/>
     <tableColumn id="12" xr3:uid="{BD311DD0-F1E1-4060-8C38-8C9EA5B490D9}" name="amount"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{78C930AD-B017-4C45-AEE5-F24DDE5263F9}" name="Table268" displayName="Table268" ref="E83:P89" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="E83:P89" xr:uid="{78C930AD-B017-4C45-AEE5-F24DDE5263F9}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{3A2544FA-2818-4005-8F9E-0316EEF33DD4}" name="trade_id"/>
+    <tableColumn id="2" xr3:uid="{20E8470A-D1B7-49D0-8A65-F566B5AC6868}" name="broker_order_id"/>
+    <tableColumn id="3" xr3:uid="{C45E3CE0-2D0B-4BBD-A90E-BD9E6257FD34}" name="exchange_order_id"/>
+    <tableColumn id="4" xr3:uid="{1384CF59-EE1A-4E07-947A-21E8DB14470E}" name="instrument"/>
+    <tableColumn id="5" xr3:uid="{97CE653F-030A-42A0-B185-C171B8D979A7}" name="instrument_key"/>
+    <tableColumn id="6" xr3:uid="{D4428138-B376-4AF1-BB7D-B70B8A9408A1}" name="side"/>
+    <tableColumn id="7" xr3:uid="{E3C19C5C-EE8F-42E0-9821-679F138A379F}" name="entry"/>
+    <tableColumn id="8" xr3:uid="{363F8B4C-3430-49DF-976F-1A87FF1F014C}" name="exit"/>
+    <tableColumn id="9" xr3:uid="{891B5180-B3BA-433B-94EE-54535269504D}" name="trailed"/>
+    <tableColumn id="10" xr3:uid="{ABEECDDD-FA35-4452-A656-B88CC00F678D}" name="timestamp"/>
+    <tableColumn id="11" xr3:uid="{2706807B-9A28-485B-B2BA-7989F3A30E1F}" name="qty"/>
+    <tableColumn id="12" xr3:uid="{E9ACB2EE-D48E-497C-8025-232002D4420D}" name="amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -719,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81522B13-2059-4C06-A47E-15A0BC3CF508}">
-  <dimension ref="D3:V80"/>
+  <dimension ref="D3:V99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
@@ -1233,13 +1295,149 @@
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
     </row>
-    <row r="80" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E80" s="5" t="s">
+    <row r="81" spans="5:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+      <c r="N81" s="8"/>
+      <c r="O81" s="8"/>
+      <c r="P81" s="8"/>
+    </row>
+    <row r="82" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+    </row>
+    <row r="83" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E83" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="O91" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
+      <c r="N93" s="7"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+    </row>
+    <row r="94" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
+      <c r="M94" s="7"/>
+      <c r="N94" s="7"/>
+      <c r="O94" s="7"/>
+      <c r="P94" s="7"/>
+    </row>
+    <row r="95" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
+      <c r="M95" s="7"/>
+      <c r="N95" s="7"/>
+      <c r="O95" s="7"/>
+      <c r="P95" s="7"/>
+    </row>
+    <row r="96" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="7"/>
+      <c r="N96" s="7"/>
+      <c r="O96" s="7"/>
+      <c r="P96" s="7"/>
+    </row>
+    <row r="99" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E99" s="5" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="E81:P81"/>
+    <mergeCell ref="E93:P96"/>
     <mergeCell ref="E60:P60"/>
     <mergeCell ref="E74:P77"/>
     <mergeCell ref="E39:P39"/>
@@ -1250,11 +1448,12 @@
     <mergeCell ref="E34:P37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="4">
+  <tableParts count="5">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/files/input/template.xlsx
+++ b/files/input/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramFiles\VM_OS\shared\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0288A32F-502F-46C9-BE70-BA408EE56C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8E4CFB-4A90-451E-951E-EC47FB27F444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31680" yWindow="2880" windowWidth="38700" windowHeight="15375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -84,7 +84,7 @@
     <t>TitanBot</t>
   </si>
   <si>
-    <t>Fibobot</t>
+    <t>FiboBot</t>
   </si>
 </sst>
 </file>
@@ -196,13 +196,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -498,21 +498,21 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{78C930AD-B017-4C45-AEE5-F24DDE5263F9}" name="Table268" displayName="Table268" ref="E83:P89" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
-  <autoFilter ref="E83:P89" xr:uid="{78C930AD-B017-4C45-AEE5-F24DDE5263F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B0683529-6857-4F8F-87DE-F47B05C4B64B}" name="Table2742" displayName="Table2742" ref="E83:P90" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="E83:P90" xr:uid="{B0683529-6857-4F8F-87DE-F47B05C4B64B}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3A2544FA-2818-4005-8F9E-0316EEF33DD4}" name="trade_id"/>
-    <tableColumn id="2" xr3:uid="{20E8470A-D1B7-49D0-8A65-F566B5AC6868}" name="broker_order_id"/>
-    <tableColumn id="3" xr3:uid="{C45E3CE0-2D0B-4BBD-A90E-BD9E6257FD34}" name="exchange_order_id"/>
-    <tableColumn id="4" xr3:uid="{1384CF59-EE1A-4E07-947A-21E8DB14470E}" name="instrument"/>
-    <tableColumn id="5" xr3:uid="{97CE653F-030A-42A0-B185-C171B8D979A7}" name="instrument_key"/>
-    <tableColumn id="6" xr3:uid="{D4428138-B376-4AF1-BB7D-B70B8A9408A1}" name="side"/>
-    <tableColumn id="7" xr3:uid="{E3C19C5C-EE8F-42E0-9821-679F138A379F}" name="entry"/>
-    <tableColumn id="8" xr3:uid="{363F8B4C-3430-49DF-976F-1A87FF1F014C}" name="exit"/>
-    <tableColumn id="9" xr3:uid="{891B5180-B3BA-433B-94EE-54535269504D}" name="trailed"/>
-    <tableColumn id="10" xr3:uid="{ABEECDDD-FA35-4452-A656-B88CC00F678D}" name="timestamp"/>
-    <tableColumn id="11" xr3:uid="{2706807B-9A28-485B-B2BA-7989F3A30E1F}" name="qty"/>
-    <tableColumn id="12" xr3:uid="{E9ACB2EE-D48E-497C-8025-232002D4420D}" name="amount"/>
+    <tableColumn id="1" xr3:uid="{20CC4563-6EE8-4760-9EF0-26174287EA52}" name="trade_id"/>
+    <tableColumn id="2" xr3:uid="{383DEF5A-47E8-46C7-8488-86C8473C4032}" name="broker_order_id"/>
+    <tableColumn id="3" xr3:uid="{2CC8B1FD-7841-43E0-9E08-A44F4A7852B0}" name="exchange_order_id"/>
+    <tableColumn id="4" xr3:uid="{D247D6E3-0DFE-4F36-854B-92D19A5FE80C}" name="instrument"/>
+    <tableColumn id="5" xr3:uid="{17973419-2332-44E0-8CF4-EDAEE8599B5A}" name="instrument_key"/>
+    <tableColumn id="6" xr3:uid="{F2590BC8-0341-48C7-8A30-23B92C471200}" name="side"/>
+    <tableColumn id="7" xr3:uid="{3F37F559-EC7A-4A80-B33F-6B6723C50F36}" name="entry"/>
+    <tableColumn id="8" xr3:uid="{C1BB9A88-8AE0-48C2-BDE9-C6FA77F41096}" name="exit"/>
+    <tableColumn id="9" xr3:uid="{4B4441DD-CE2C-4CC9-BA11-27FC230AB1C6}" name="trailed"/>
+    <tableColumn id="10" xr3:uid="{35685DD2-8547-4331-980D-994D1BD255FA}" name="timestamp"/>
+    <tableColumn id="11" xr3:uid="{6ABAF89F-7B3D-45D9-83F8-AF2D2DF68AD8}" name="qty"/>
+    <tableColumn id="12" xr3:uid="{00912DE2-5D1E-49AD-AE6C-F04D9D1808AF}" name="amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -795,20 +795,20 @@
   </cols>
   <sheetData>
     <row r="3" spans="4:22" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="4:22" x14ac:dyDescent="0.3">
       <c r="D4" s="1"/>
@@ -936,20 +936,20 @@
       <c r="P18" s="7"/>
     </row>
     <row r="22" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
     </row>
     <row r="24" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E24" s="2" t="s">
@@ -1056,20 +1056,20 @@
       <c r="P37" s="7"/>
     </row>
     <row r="39" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
     </row>
     <row r="41" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E41" s="2" t="s">
@@ -1176,20 +1176,20 @@
       <c r="P56" s="7"/>
     </row>
     <row r="60" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
     </row>
     <row r="62" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E62" s="2" t="s">
@@ -1295,7 +1295,7 @@
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
     </row>
-    <row r="81" spans="5:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E81" s="8" t="s">
         <v>19</v>
       </c>
@@ -1310,20 +1310,6 @@
       <c r="N81" s="8"/>
       <c r="O81" s="8"/>
       <c r="P81" s="8"/>
-    </row>
-    <row r="82" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
-      <c r="P82" s="1"/>
     </row>
     <row r="83" spans="5:16" x14ac:dyDescent="0.3">
       <c r="E83" s="2" t="s">
@@ -1436,16 +1422,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E3:P3"/>
+    <mergeCell ref="E15:P18"/>
+    <mergeCell ref="E22:P22"/>
+    <mergeCell ref="E34:P37"/>
     <mergeCell ref="E81:P81"/>
     <mergeCell ref="E93:P96"/>
     <mergeCell ref="E60:P60"/>
     <mergeCell ref="E74:P77"/>
     <mergeCell ref="E39:P39"/>
     <mergeCell ref="E53:P56"/>
-    <mergeCell ref="E3:P3"/>
-    <mergeCell ref="E15:P18"/>
-    <mergeCell ref="E22:P22"/>
-    <mergeCell ref="E34:P37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="5">
